--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22580" windowHeight="11270"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11820"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,73 +14,127 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+  <x:si>
+    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 공격의 배율 리스트(스킬데이터로 빠질수 있음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.5,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillAtkMultiple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 공격 스킬 배율(기본공격 배율)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalAtkMultiple</x:t>
+  </x:si>
   <x:si>
     <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
+    <x:t>곰 아저씨다. 매일 이 시간에 보인다 . 백수인가 보다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
   </x:si>
   <x:si>
     <x:t>몬스터 설명 (도감용)</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_pigme_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>몬스터 표기용 Icon</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+    <x:t>Icon/Icon_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰저씨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float[ ]</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -117,6 +166,11 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
       <x:name val="&quot;맑은 고딕&quot;"/>
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
@@ -142,7 +196,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -172,12 +225,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd2f2db"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="3">
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left>
         <x:color rgb="ff000000"/>
       </x:left>
@@ -185,27 +237,33 @@
         <x:color rgb="ff000000"/>
       </x:right>
       <x:top>
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom>
         <x:color rgb="ff000000"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:left>
       <x:right style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:right>
       <x:top style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="thin">
         <x:color rgb="ff000000"/>
       </x:left>
@@ -218,36 +276,81 @@
       <x:bottom style="thin">
         <x:color rgb="ff000000"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -262,7 +365,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -274,20 +377,22 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
+    <x:cellStyle xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="12">
+  <x:dxfs count="30">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -370,7 +475,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -405,7 +509,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -450,7 +553,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -494,7 +596,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -502,10 +603,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -514,10 +615,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -529,10 +630,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -541,10 +642,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -579,7 +680,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -600,7 +700,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -631,15 +730,52 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
             <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
             <hs:offset val="0"/>
           </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
           <x:border>
-            <x:bottom style="medium">
-              <x:color rgb="ff6182d6"/>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
             </x:bottom>
           </x:border>
         </x:dxf>
@@ -647,16 +783,429 @@
       <mc:Fallback>
         <x:dxf>
           <x:font>
-            <x:b val="1"/>
-          </x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
           <x:border>
-            <x:bottom style="medium">
-              <x:color rgb="ff6182d6"/>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
             </x:bottom>
           </x:border>
         </x:dxf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:left style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:left>
+        <x:right style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:right>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
   <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
@@ -685,7 +1234,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -880,108 +1429,161 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:O35"/>
+  <x:sheetPr codeName="Sheet1"/>
+  <x:dimension ref="A1:S35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="50.7265625" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="20.26953125" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="7" max="16384" width="12.54296875" style="3"/>
+    <x:col min="4" max="4" width="33.71484375" style="3" customWidth="1"/>
+    <x:col min="5" max="5" width="32.4296875" style="3" customWidth="1"/>
+    <x:col min="6" max="6" width="33.85546875" style="3" customWidth="1"/>
+    <x:col min="7" max="7" width="36.14453125" style="3" customWidth="1"/>
+    <x:col min="8" max="8" width="20.26953125" style="3" customWidth="1"/>
+    <x:col min="9" max="9" width="30.54296875" style="3" customWidth="1"/>
+    <x:col min="10" max="10" width="26.54296875" style="3" customWidth="1"/>
+    <x:col min="11" max="12" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10" ht="12.300000000000001">
+      <x:c r="A2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3" spans="1:11" s="13" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="12" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J3" s="15"/>
+      <x:c r="K3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
+      <x:c r="A4" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="16">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E4" s="17">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="17">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G4" s="17">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H4" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.19999999999999928946">
-      <x:c r="A2" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F2" s="1"/>
-    </x:row>
-    <x:row r="3" spans="1:6" s="13" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3" s="15"/>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D4" s="5"/>
-      <x:c r="E4" s="5"/>
-      <x:c r="F4" s="16"/>
-      <x:c r="G4" s="5"/>
-      <x:c r="H4" s="5"/>
-      <x:c r="I4" s="5"/>
-      <x:c r="J4" s="5"/>
+      <x:c r="J4" s="16"/>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5"/>
       <x:c r="M4" s="5"/>
       <x:c r="N4" s="5"/>
       <x:c r="O4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P4" s="5"/>
+      <x:c r="Q4" s="5"/>
+      <x:c r="R4" s="5"/>
+      <x:c r="S4" s="5"/>
+    </x:row>
+    <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="5"/>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="5"/>
+      <x:c r="E5" s="17"/>
+      <x:c r="F5" s="17"/>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
@@ -991,20 +1593,24 @@
       <x:c r="M5" s="5"/>
       <x:c r="N5" s="5"/>
       <x:c r="O5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P5" s="5"/>
+      <x:c r="Q5" s="5"/>
+      <x:c r="R5" s="5"/>
+      <x:c r="S5" s="5"/>
+    </x:row>
+    <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="5"/>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5"/>
+      <x:c r="E6" s="17"/>
+      <x:c r="F6" s="17"/>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
@@ -1014,32 +1620,58 @@
       <x:c r="M6" s="5"/>
       <x:c r="N6" s="5"/>
       <x:c r="O6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="4"/>
-      <x:c r="B7" s="4"/>
-      <x:c r="C7" s="4"/>
-      <x:c r="D7" s="5"/>
-      <x:c r="E7" s="5"/>
-      <x:c r="F7" s="5"/>
-      <x:c r="G7" s="5"/>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="5"/>
+      <x:c r="P6" s="5"/>
+      <x:c r="Q6" s="5"/>
+      <x:c r="R6" s="5"/>
+      <x:c r="S6" s="5"/>
+    </x:row>
+    <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
+      <x:c r="A7" s="6" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D7" s="5">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="E7" s="17">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F7" s="17">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G7" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>
       <x:c r="M7" s="5"/>
       <x:c r="N7" s="5"/>
       <x:c r="O7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P7" s="5"/>
+      <x:c r="Q7" s="5"/>
+      <x:c r="R7" s="5"/>
+      <x:c r="S7" s="5"/>
+    </x:row>
+    <x:row r="8" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A8" s="7"/>
       <x:c r="B8" s="7"/>
       <x:c r="C8" s="7"/>
-      <x:c r="D8" s="5"/>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="5"/>
-      <x:c r="G8" s="5"/>
+      <x:c r="D8" s="7"/>
+      <x:c r="E8" s="7"/>
+      <x:c r="F8" s="7"/>
+      <x:c r="G8" s="7"/>
       <x:c r="H8" s="5"/>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="5"/>
@@ -1048,15 +1680,19 @@
       <x:c r="M8" s="5"/>
       <x:c r="N8" s="5"/>
       <x:c r="O8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P8" s="5"/>
+      <x:c r="Q8" s="5"/>
+      <x:c r="R8" s="5"/>
+      <x:c r="S8" s="5"/>
+    </x:row>
+    <x:row r="9" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A9" s="7"/>
       <x:c r="B9" s="7"/>
       <x:c r="C9" s="7"/>
-      <x:c r="D9" s="5"/>
-      <x:c r="E9" s="5"/>
-      <x:c r="F9" s="5"/>
-      <x:c r="G9" s="5"/>
+      <x:c r="D9" s="7"/>
+      <x:c r="E9" s="7"/>
+      <x:c r="F9" s="7"/>
+      <x:c r="G9" s="7"/>
       <x:c r="H9" s="5"/>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="5"/>
@@ -1065,15 +1701,19 @@
       <x:c r="M9" s="5"/>
       <x:c r="N9" s="5"/>
       <x:c r="O9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P9" s="5"/>
+      <x:c r="Q9" s="5"/>
+      <x:c r="R9" s="5"/>
+      <x:c r="S9" s="5"/>
+    </x:row>
+    <x:row r="10" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1"/>
       <x:c r="C10" s="1"/>
-      <x:c r="D10" s="5"/>
-      <x:c r="E10" s="5"/>
-      <x:c r="F10" s="5"/>
-      <x:c r="G10" s="5"/>
+      <x:c r="D10" s="1"/>
+      <x:c r="E10" s="1"/>
+      <x:c r="F10" s="1"/>
+      <x:c r="G10" s="1"/>
       <x:c r="H10" s="5"/>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5"/>
@@ -1082,15 +1722,19 @@
       <x:c r="M10" s="5"/>
       <x:c r="N10" s="5"/>
       <x:c r="O10" s="5"/>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P10" s="5"/>
+      <x:c r="Q10" s="5"/>
+      <x:c r="R10" s="5"/>
+      <x:c r="S10" s="5"/>
+    </x:row>
+    <x:row r="11" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
       <x:c r="C11" s="1"/>
-      <x:c r="D11" s="5"/>
-      <x:c r="E11" s="5"/>
-      <x:c r="F11" s="5"/>
-      <x:c r="G11" s="5"/>
+      <x:c r="D11" s="1"/>
+      <x:c r="E11" s="1"/>
+      <x:c r="F11" s="1"/>
+      <x:c r="G11" s="1"/>
       <x:c r="H11" s="5"/>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5"/>
@@ -1099,15 +1743,19 @@
       <x:c r="M11" s="5"/>
       <x:c r="N11" s="5"/>
       <x:c r="O11" s="5"/>
-    </x:row>
-    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P11" s="5"/>
+      <x:c r="Q11" s="5"/>
+      <x:c r="R11" s="5"/>
+      <x:c r="S11" s="5"/>
+    </x:row>
+    <x:row r="12" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A12" s="7"/>
       <x:c r="B12" s="7"/>
       <x:c r="C12" s="7"/>
-      <x:c r="D12" s="5"/>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5"/>
-      <x:c r="G12" s="5"/>
+      <x:c r="D12" s="7"/>
+      <x:c r="E12" s="7"/>
+      <x:c r="F12" s="7"/>
+      <x:c r="G12" s="7"/>
       <x:c r="H12" s="5"/>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5"/>
@@ -1116,15 +1764,19 @@
       <x:c r="M12" s="5"/>
       <x:c r="N12" s="5"/>
       <x:c r="O12" s="5"/>
-    </x:row>
-    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P12" s="5"/>
+      <x:c r="Q12" s="5"/>
+      <x:c r="R12" s="5"/>
+      <x:c r="S12" s="5"/>
+    </x:row>
+    <x:row r="13" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A13" s="4"/>
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="4"/>
-      <x:c r="D13" s="5"/>
-      <x:c r="E13" s="5"/>
-      <x:c r="F13" s="5"/>
-      <x:c r="G13" s="5"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
       <x:c r="H13" s="5"/>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5"/>
@@ -1133,15 +1785,19 @@
       <x:c r="M13" s="5"/>
       <x:c r="N13" s="5"/>
       <x:c r="O13" s="5"/>
-    </x:row>
-    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P13" s="5"/>
+      <x:c r="Q13" s="5"/>
+      <x:c r="R13" s="5"/>
+      <x:c r="S13" s="5"/>
+    </x:row>
+    <x:row r="14" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
       <x:c r="C14" s="1"/>
-      <x:c r="D14" s="5"/>
-      <x:c r="E14" s="5"/>
-      <x:c r="F14" s="5"/>
-      <x:c r="G14" s="5"/>
+      <x:c r="D14" s="1"/>
+      <x:c r="E14" s="1"/>
+      <x:c r="F14" s="1"/>
+      <x:c r="G14" s="1"/>
       <x:c r="H14" s="5"/>
       <x:c r="I14" s="5"/>
       <x:c r="J14" s="5"/>
@@ -1150,15 +1806,19 @@
       <x:c r="M14" s="5"/>
       <x:c r="N14" s="5"/>
       <x:c r="O14" s="5"/>
-    </x:row>
-    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P14" s="5"/>
+      <x:c r="Q14" s="5"/>
+      <x:c r="R14" s="5"/>
+      <x:c r="S14" s="5"/>
+    </x:row>
+    <x:row r="15" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
       <x:c r="C15" s="1"/>
-      <x:c r="D15" s="5"/>
-      <x:c r="E15" s="5"/>
-      <x:c r="F15" s="5"/>
-      <x:c r="G15" s="5"/>
+      <x:c r="D15" s="1"/>
+      <x:c r="E15" s="1"/>
+      <x:c r="F15" s="1"/>
+      <x:c r="G15" s="1"/>
       <x:c r="H15" s="5"/>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="5"/>
@@ -1167,112 +1827,196 @@
       <x:c r="M15" s="5"/>
       <x:c r="N15" s="5"/>
       <x:c r="O15" s="5"/>
-    </x:row>
-    <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="P15" s="5"/>
+      <x:c r="Q15" s="5"/>
+      <x:c r="R15" s="5"/>
+      <x:c r="S15" s="5"/>
+    </x:row>
+    <x:row r="16" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A16" s="8"/>
       <x:c r="B16" s="8"/>
       <x:c r="C16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D16" s="8"/>
+      <x:c r="E16" s="8"/>
+      <x:c r="F16" s="8"/>
+      <x:c r="G16" s="8"/>
+    </x:row>
+    <x:row r="17" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A17" s="9"/>
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="9"/>
-    </x:row>
-    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D17" s="8"/>
+      <x:c r="E17" s="8"/>
+      <x:c r="F17" s="8"/>
+      <x:c r="G17" s="8"/>
+    </x:row>
+    <x:row r="18" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A18" s="9"/>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D18" s="8"/>
+      <x:c r="E18" s="8"/>
+      <x:c r="F18" s="8"/>
+      <x:c r="G18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
-      <x:c r="D19" s="5"/>
-      <x:c r="E19" s="5"/>
-    </x:row>
-    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D19" s="8"/>
+      <x:c r="E19" s="8"/>
+      <x:c r="F19" s="8"/>
+      <x:c r="G19" s="8"/>
+      <x:c r="H19" s="5"/>
+      <x:c r="I19" s="5"/>
+    </x:row>
+    <x:row r="20" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A20" s="9"/>
       <x:c r="B20" s="9"/>
       <x:c r="C20" s="9"/>
-    </x:row>
-    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D20" s="8"/>
+      <x:c r="E20" s="8"/>
+      <x:c r="F20" s="8"/>
+      <x:c r="G20" s="8"/>
+    </x:row>
+    <x:row r="21" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A21" s="9"/>
       <x:c r="B21" s="9"/>
       <x:c r="C21" s="9"/>
-    </x:row>
-    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D21" s="8"/>
+      <x:c r="E21" s="8"/>
+      <x:c r="F21" s="8"/>
+      <x:c r="G21" s="8"/>
+    </x:row>
+    <x:row r="22" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A22" s="9"/>
       <x:c r="B22" s="9"/>
       <x:c r="C22" s="9"/>
-    </x:row>
-    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D22" s="8"/>
+      <x:c r="E22" s="8"/>
+      <x:c r="F22" s="8"/>
+      <x:c r="G22" s="8"/>
+    </x:row>
+    <x:row r="23" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A23" s="9"/>
       <x:c r="B23" s="9"/>
       <x:c r="C23" s="9"/>
-    </x:row>
-    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D23" s="8"/>
+      <x:c r="E23" s="8"/>
+      <x:c r="F23" s="8"/>
+      <x:c r="G23" s="8"/>
+    </x:row>
+    <x:row r="24" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A24" s="9"/>
       <x:c r="B24" s="9"/>
       <x:c r="C24" s="9"/>
-    </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D24" s="8"/>
+      <x:c r="E24" s="8"/>
+      <x:c r="F24" s="8"/>
+      <x:c r="G24" s="8"/>
+    </x:row>
+    <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A25" s="9"/>
       <x:c r="B25" s="9"/>
       <x:c r="C25" s="9"/>
-      <x:c r="E25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D25" s="8"/>
+      <x:c r="E25" s="8"/>
+      <x:c r="F25" s="8"/>
+      <x:c r="G25" s="8"/>
+      <x:c r="I25" s="5"/>
+    </x:row>
+    <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A26" s="10"/>
       <x:c r="B26" s="10"/>
       <x:c r="C26" s="10"/>
-      <x:c r="E26" s="5"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D26" s="10"/>
+      <x:c r="E26" s="10"/>
+      <x:c r="F26" s="10"/>
+      <x:c r="G26" s="10"/>
+      <x:c r="I26" s="5"/>
+    </x:row>
+    <x:row r="27" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A27" s="10"/>
       <x:c r="B27" s="10"/>
       <x:c r="C27" s="10"/>
-      <x:c r="E27" s="5"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D27" s="10"/>
+      <x:c r="E27" s="10"/>
+      <x:c r="F27" s="10"/>
+      <x:c r="G27" s="10"/>
+      <x:c r="I27" s="5"/>
+    </x:row>
+    <x:row r="28" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A28" s="10"/>
       <x:c r="B28" s="10"/>
       <x:c r="C28" s="10"/>
-      <x:c r="E28" s="5"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D28" s="10"/>
+      <x:c r="E28" s="10"/>
+      <x:c r="F28" s="10"/>
+      <x:c r="G28" s="10"/>
+      <x:c r="I28" s="5"/>
+    </x:row>
+    <x:row r="29" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A29" s="10"/>
       <x:c r="B29" s="10"/>
       <x:c r="C29" s="10"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D29" s="10"/>
+      <x:c r="E29" s="10"/>
+      <x:c r="F29" s="10"/>
+      <x:c r="G29" s="10"/>
+    </x:row>
+    <x:row r="30" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A30" s="10"/>
       <x:c r="B30" s="10"/>
       <x:c r="C30" s="10"/>
-    </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D30" s="10"/>
+      <x:c r="E30" s="10"/>
+      <x:c r="F30" s="10"/>
+      <x:c r="G30" s="10"/>
+    </x:row>
+    <x:row r="31" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A31" s="10"/>
       <x:c r="B31" s="10"/>
       <x:c r="C31" s="10"/>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D31" s="10"/>
+      <x:c r="E31" s="10"/>
+      <x:c r="F31" s="10"/>
+      <x:c r="G31" s="10"/>
+    </x:row>
+    <x:row r="32" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A32" s="11"/>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="11"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D32" s="11"/>
+      <x:c r="E32" s="11"/>
+      <x:c r="F32" s="11"/>
+      <x:c r="G32" s="11"/>
+    </x:row>
+    <x:row r="33" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A33" s="11"/>
       <x:c r="B33" s="11"/>
       <x:c r="C33" s="11"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D33" s="11"/>
+      <x:c r="E33" s="11"/>
+      <x:c r="F33" s="11"/>
+      <x:c r="G33" s="11"/>
+    </x:row>
+    <x:row r="34" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A34" s="11"/>
       <x:c r="B34" s="11"/>
       <x:c r="C34" s="11"/>
-    </x:row>
-    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D34" s="11"/>
+      <x:c r="E34" s="11"/>
+      <x:c r="F34" s="11"/>
+      <x:c r="G34" s="11"/>
+    </x:row>
+    <x:row r="35" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A35" s="11"/>
       <x:c r="B35" s="11"/>
       <x:c r="C35" s="11"/>
+      <x:c r="D35" s="11"/>
+      <x:c r="E35" s="11"/>
+      <x:c r="F35" s="11"/>
+      <x:c r="G35" s="11"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>
@@ -2240,7 +2984,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -16,118 +16,118 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <x:si>
+    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰 아저씨다. 매일 이 시간에 보인다 . 백수인가 보다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 공격의 배율 리스트(스킬데이터로 빠질수 있음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
     <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬 공격의 배율 리스트(스킬데이터로 빠질수 있음)</x:t>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 공격 스킬 배율(기본공격 배율)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰저씨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float[ ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillAtkMultiple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalAtkMultiple</x:t>
   </x:si>
   <x:si>
     <x:t>1.5,5</x:t>
   </x:si>
   <x:si>
-    <x:t>2DObject/Monster_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DObject/Monster_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillAtkMultiple</x:t>
-  </x:si>
-  <x:si>
     <x:t>BaseHP</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>float</x:t>
   </x:si>
   <x:si>
     <x:t>기본 공격력</x:t>
   </x:si>
   <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 공격 스킬 배율(기본공격 배율)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalAtkMultiple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰 아저씨다. 매일 이 시간에 보인다 . 백수인가 보다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
   </x:si>
   <x:si>
     <x:t>슬라이무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_bear_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_pigme_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰저씨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float[ ]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1449,98 +1449,98 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F1" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:11" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
+      <x:c r="I3" s="14" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I3" s="14" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="J3" s="15"/>
       <x:c r="K3" s="3"/>
     </x:row>
     <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D4" s="16">
         <x:v>500</x:v>
@@ -1555,10 +1555,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J4" s="16"/>
       <x:c r="K4" s="5"/>
@@ -1573,13 +1573,13 @@
     </x:row>
     <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="17"/>
@@ -1600,13 +1600,13 @@
     </x:row>
     <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="5"/>
       <x:c r="E6" s="17"/>
@@ -1627,15 +1627,15 @@
     </x:row>
     <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="17">
         <x:v>1500</x:v>
       </x:c>
       <x:c r="E7" s="17">
@@ -1645,13 +1645,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G7" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -16,118 +16,118 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <x:si>
+    <x:t>2DObject/Monster_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 공격 스킬 배율(기본공격 배율)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalAtkMultiple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰저씨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미</x:t>
+  </x:si>
+  <x:si>
     <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
   </x:si>
   <x:si>
+    <x:t>스킬 공격의 배율 리스트(스킬데이터로 빠질수 있음)</x:t>
+  </x:si>
+  <x:si>
     <x:t>곰 아저씨다. 매일 이 시간에 보인다 . 백수인가 보다</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬 공격의 배율 리스트(스킬데이터로 빠질수 있음)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.5,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>mob_bear_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float[ ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
   </x:si>
   <x:si>
     <x:t>몬스터 설명 (도감용)</x:t>
   </x:si>
   <x:si>
-    <x:t>일반 공격 스킬 배율(기본공격 배율)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DObject/Monster_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DObject/Monster_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰저씨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Bear</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float[ ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_bear_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_pigme_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillAtkMultiple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalAtkMultiple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.5,5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseHP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무</x:t>
+    <x:t>SkillAtkMultipleList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -393,6 +393,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -475,6 +476,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -509,6 +511,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -553,6 +556,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -596,6 +600,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -680,6 +685,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -700,6 +706,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -730,6 +737,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1449,98 +1457,98 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F1" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:11" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I3" s="14" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J3" s="15"/>
       <x:c r="K3" s="3"/>
     </x:row>
     <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="16">
         <x:v>500</x:v>
@@ -1555,10 +1563,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J4" s="16"/>
       <x:c r="K4" s="5"/>
@@ -1573,13 +1581,13 @@
     </x:row>
     <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="17"/>
@@ -1600,13 +1608,13 @@
     </x:row>
     <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="5"/>
       <x:c r="E6" s="17"/>
@@ -1627,13 +1635,13 @@
     </x:row>
     <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="17">
         <x:v>1500</x:v>
@@ -1645,13 +1653,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G7" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5"/>
